--- a/DNLI.xlsx
+++ b/DNLI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA87285-B456-4315-B9F8-B2729220EB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5E0437-E914-42C9-9042-093230A98088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38450" yWindow="2510" windowWidth="17780" windowHeight="16580" xr2:uid="{AD0EA94E-C078-9049-B35D-03F39FBC1664}"/>
+    <workbookView xWindow="15230" yWindow="2630" windowWidth="22360" windowHeight="16580" xr2:uid="{AD0EA94E-C078-9049-B35D-03F39FBC1664}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>Price</t>
   </si>
@@ -99,9 +99,6 @@
     <t>DNL126</t>
   </si>
   <si>
-    <t>Sanfilippo</t>
-  </si>
-  <si>
     <t>SGSH ERT</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>Phase</t>
   </si>
   <si>
-    <t>DNL310 (tividenofusp alfa)</t>
-  </si>
-  <si>
     <t>Multiple Sclerosis</t>
   </si>
   <si>
@@ -159,9 +153,6 @@
     <t>BIIB</t>
   </si>
   <si>
-    <t>Filed</t>
-  </si>
-  <si>
     <t>I</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>Brand</t>
   </si>
   <si>
-    <t>DNL310, ETV:IDS</t>
-  </si>
-  <si>
     <t>Generic</t>
   </si>
   <si>
@@ -201,14 +189,53 @@
     <t>ATV:Abeta</t>
   </si>
   <si>
-    <t>Q125</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Avlayah (tividenofusp alfa)</t>
+  </si>
+  <si>
+    <t>Avlayah fka DNL310, ETV:IDS</t>
+  </si>
+  <si>
+    <t>Approval</t>
+  </si>
+  <si>
+    <t>DNL628</t>
+  </si>
+  <si>
+    <t>OTV:MAPT</t>
+  </si>
+  <si>
+    <t>TAK returned rights</t>
+  </si>
+  <si>
+    <t>Sanfilippo A</t>
+  </si>
+  <si>
+    <t>III preparing</t>
+  </si>
+  <si>
+    <t>I/II results by YE26</t>
+  </si>
+  <si>
+    <t>Pompe</t>
+  </si>
+  <si>
+    <t>DNL952</t>
+  </si>
+  <si>
+    <t>DNL111</t>
+  </si>
+  <si>
+    <t>Gaucher/Parkinsons</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -251,6 +278,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -359,16 +393,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -378,10 +409,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -699,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691F9766-64C5-8B4D-9607-C42434172F4A}">
-  <dimension ref="B2:L15"/>
+  <dimension ref="B2:S15"/>
   <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.08203125" style="1" customWidth="1"/>
@@ -712,34 +750,34 @@
     <col min="13" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
+      <c r="E2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="2">
-        <v>14.14</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
-        <v>35</v>
+        <v>25.69</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B3" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -747,67 +785,73 @@
       <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>40</v>
+      <c r="F3" s="16">
+        <v>46082</v>
       </c>
       <c r="H3" s="5"/>
       <c r="J3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>171.22202999999999</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5"/>
+        <f>158.709+28.331</f>
+        <v>187.04</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B4" s="17"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
       <c r="J4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="3">
         <f>K2*K3</f>
-        <v>2421.0795042</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>4805.0576000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="13" x14ac:dyDescent="0.3">
+      <c r="B5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>11</v>
       </c>
       <c r="H5" s="5"/>
       <c r="J5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="3">
-        <f>56.947+760.979+235.844</f>
-        <v>1053.77</v>
-      </c>
-      <c r="L5" s="12" t="s">
+        <f>387.626+600.058+63.785</f>
+        <v>1051.4690000000001</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
+      <c r="D6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="H6" s="5"/>
       <c r="J6" s="1" t="s">
@@ -816,19 +860,22 @@
       <c r="K6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>53</v>
+      <c r="L6" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="H7" s="5"/>
       <c r="J7" s="1" t="s">
@@ -836,102 +883,143 @@
       </c>
       <c r="K7" s="3">
         <f>K4-K5+K6</f>
-        <v>1367.3095042</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>41</v>
+        <v>3753.5886</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="13" x14ac:dyDescent="0.3">
+      <c r="B8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>37</v>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="H9" s="5"/>
       <c r="J9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="13" t="s">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="5"/>
+      <c r="Q11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="3">
+        <v>2704.9920000000002</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" ht="13" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="E12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="J11" s="13" t="s">
+      <c r="F12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
+      <c r="J12" s="10" t="s">
         <v>32</v>
-      </c>
-      <c r="K11" s="3">
-        <v>2704.9920000000002</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="J12" s="13" t="s">
-        <v>33</v>
       </c>
       <c r="K12" s="3">
         <v>1317.039</v>
       </c>
-      <c r="L12" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="J15" s="13" t="s">
-        <v>42</v>
+      <c r="L12" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="13" x14ac:dyDescent="0.3">
+      <c r="B13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" spans="2:19" ht="13" x14ac:dyDescent="0.3">
+      <c r="B14" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J15" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -947,53 +1035,53 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.08203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.58203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" style="13"/>
+    <col min="1" max="1" width="5.08203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.58203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="13" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="13" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C9" s="13" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C6" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C9" s="17" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
